--- a/result.xlsx
+++ b/result.xlsx
@@ -7,12 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accuracy" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NRMSE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="angle" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b_error" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d_move_avg" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accuracy" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NRMSE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="angle" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b_error" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="make_fake_data time" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fitting_time" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,16 +434,16 @@
         <v>0.1</v>
       </c>
       <c r="C1" t="n">
-        <v>1</v>
+        <v>0.3162277660168379</v>
       </c>
       <c r="D1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" t="n">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="F1" t="n">
         <v>10</v>
-      </c>
-      <c r="E1" t="n">
-        <v>100</v>
-      </c>
-      <c r="F1" t="n">
-        <v>1000</v>
       </c>
     </row>
     <row r="2">
@@ -448,7 +451,19 @@
         <v>0.05</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8012820512820513</v>
+        <v>0.04973382272944051</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0496941214119279</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.04966724474469342</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.04958910346246385</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04959082995692098</v>
       </c>
     </row>
     <row r="3">
@@ -456,7 +471,19 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8012820512820513</v>
+        <v>0.09945512479857301</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.09938593718513218</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.09933145711344617</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.09917345343464246</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.09918165991384198</v>
       </c>
     </row>
     <row r="4">
@@ -464,42 +491,159 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8012820512820513</v>
+        <v>0.1491711766131625</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1490630098852681</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1489929854892833</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1487479017113975</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.148772489870763</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>0.2</v>
       </c>
+      <c r="B5" t="n">
+        <v>0.1988716981671778</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1987343779278482</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1986479902125079</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1983245149343368</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.198363319827684</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>0.25</v>
       </c>
+      <c r="B6" t="n">
+        <v>0.2485725728894002</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2483988098394829</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.24830071741142</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2479019924116305</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2479541497846049</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>0.3</v>
       </c>
+      <c r="B7" t="n">
+        <v>0.2982666866635883</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.2980520136751268</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2979407508984738</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2974799023101051</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2975449797415259</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>0.35</v>
       </c>
+      <c r="B8" t="n">
+        <v>0.3479504683245834</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.3476999000499341</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3475671694949371</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.3470580594775449</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3471345885545314</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>0.4</v>
       </c>
+      <c r="B9" t="n">
+        <v>0.3976372690764805</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.3973497368166813</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3971882521571894</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.3966359901715881</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3967098925819563</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>0.45</v>
       </c>
+      <c r="B10" t="n">
+        <v>0.4473229351725057</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.4469976641845472</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4468098191802465</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.4462044879088972</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4462866189358381</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>0.5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.4970026813950389</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.4966452980007652</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4964341519587417</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.4957740529598201</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4958643772148417</v>
       </c>
     </row>
   </sheetData>
@@ -526,16 +670,16 @@
         <v>0.1</v>
       </c>
       <c r="C1" t="n">
-        <v>1</v>
+        <v>0.3162277660168379</v>
       </c>
       <c r="D1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" t="n">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="F1" t="n">
         <v>10</v>
-      </c>
-      <c r="E1" t="n">
-        <v>100</v>
-      </c>
-      <c r="F1" t="n">
-        <v>1000</v>
       </c>
     </row>
     <row r="2">
@@ -543,7 +687,19 @@
         <v>0.05</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9957264957264957</v>
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9912280701754386</v>
       </c>
     </row>
     <row r="3">
@@ -551,7 +707,19 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9957264957264957</v>
+        <v>0.9736842105263158</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9912280701754386</v>
       </c>
     </row>
     <row r="4">
@@ -559,42 +727,159 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9957264957264957</v>
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9912280701754386</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>0.2</v>
       </c>
+      <c r="B5" t="n">
+        <v>0.9736842105263158</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9912280701754386</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>0.25</v>
       </c>
+      <c r="B6" t="n">
+        <v>0.9736842105263158</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9912280701754386</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>0.3</v>
       </c>
+      <c r="B7" t="n">
+        <v>0.9736842105263158</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9912280701754386</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>0.35</v>
       </c>
+      <c r="B8" t="n">
+        <v>0.9736842105263158</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9912280701754386</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>0.4</v>
       </c>
+      <c r="B9" t="n">
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9912280701754386</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>0.45</v>
       </c>
+      <c r="B10" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9736842105263158</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9912280701754386</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>0.5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.9736842105263158</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9736842105263158</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9824561403508771</v>
       </c>
     </row>
   </sheetData>
@@ -621,16 +906,16 @@
         <v>0.1</v>
       </c>
       <c r="C1" t="n">
-        <v>1</v>
+        <v>0.3162277660168379</v>
       </c>
       <c r="D1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" t="n">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="F1" t="n">
         <v>10</v>
-      </c>
-      <c r="E1" t="n">
-        <v>100</v>
-      </c>
-      <c r="F1" t="n">
-        <v>1000</v>
       </c>
     </row>
     <row r="2">
@@ -638,7 +923,19 @@
         <v>0.05</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01204387980437341</v>
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -646,7 +943,19 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01930597277163146</v>
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -654,42 +963,159 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.02775628171847976</v>
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>0.2</v>
       </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>0.25</v>
       </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>0.3</v>
       </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>0.35</v>
       </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>0.4</v>
       </c>
+      <c r="B9" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>0.45</v>
       </c>
+      <c r="B10" t="n">
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>0.5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9912280701754386</v>
       </c>
     </row>
   </sheetData>
@@ -716,16 +1142,16 @@
         <v>0.1</v>
       </c>
       <c r="C1" t="n">
-        <v>1</v>
+        <v>0.3162277660168379</v>
       </c>
       <c r="D1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" t="n">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="F1" t="n">
         <v>10</v>
-      </c>
-      <c r="E1" t="n">
-        <v>100</v>
-      </c>
-      <c r="F1" t="n">
-        <v>1000</v>
       </c>
     </row>
     <row r="2">
@@ -733,7 +1159,19 @@
         <v>0.05</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9987842195938357</v>
+        <v>0.01388265834359147</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.01660896964966888</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0237536361962975</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.04935041724028678</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.08721416599164956</v>
       </c>
     </row>
     <row r="3">
@@ -741,7 +1179,19 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9959187294429525</v>
+        <v>0.02291970420499599</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.01866564256732867</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.03920870263834449</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.05190552647723799</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1314170214577547</v>
       </c>
     </row>
     <row r="4">
@@ -749,42 +1199,159 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.991415864627104</v>
+        <v>0.02799239439445461</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.02424042862853651</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.05095767810485526</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.03143810829016403</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1006221740321114</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>0.2</v>
       </c>
+      <c r="B5" t="n">
+        <v>0.02666316666970603</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0268885325481041</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.04759242589050743</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.04249677086469794</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08567388789814595</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>0.25</v>
       </c>
+      <c r="B6" t="n">
+        <v>0.03442742237585895</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.02405403102903651</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0475350477784308</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.03982745761573755</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1598423801667478</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>0.3</v>
       </c>
+      <c r="B7" t="n">
+        <v>0.03859457734611331</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.02379291464548931</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.07156540858006948</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.04045959710199028</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1385301189892327</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>0.35</v>
       </c>
+      <c r="B8" t="n">
+        <v>0.03366495566365462</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.03054303455767724</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.07486636980340258</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.04460127213520648</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1306654538009248</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>0.4</v>
       </c>
+      <c r="B9" t="n">
+        <v>0.03940364610018948</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.045070623306933</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.09072201786663601</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.06633983852559551</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1390272747859626</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>0.45</v>
       </c>
+      <c r="B10" t="n">
+        <v>0.04322193873500723</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.04210860164317956</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0722004725080929</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.05555810598875646</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1397706022396007</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>0.5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.04481637027976349</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.04030730114602491</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.05248304574755577</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.06166126922397411</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1023077839855843</v>
       </c>
     </row>
   </sheetData>
@@ -811,16 +1378,16 @@
         <v>0.1</v>
       </c>
       <c r="C1" t="n">
-        <v>1</v>
+        <v>0.3162277660168379</v>
       </c>
       <c r="D1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" t="n">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="F1" t="n">
         <v>10</v>
-      </c>
-      <c r="E1" t="n">
-        <v>100</v>
-      </c>
-      <c r="F1" t="n">
-        <v>1000</v>
       </c>
     </row>
     <row r="2">
@@ -828,7 +1395,19 @@
         <v>0.05</v>
       </c>
       <c r="B2" t="n">
-        <v>2.825590427239935</v>
+        <v>0.9998215096933744</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.9996818123700031</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9989804203236772</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9971102508753517</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9895644702401225</v>
       </c>
     </row>
     <row r="3">
@@ -836,7 +1415,19 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>5.178251504853614</v>
+        <v>0.9997004201742751</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9990158388197172</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9969989609066638</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9930146213937093</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9745835176891159</v>
       </c>
     </row>
     <row r="4">
@@ -844,42 +1435,159 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>7.512717691533354</v>
+        <v>0.9994439563552352</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9979707877786265</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9953567669649486</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.989286330915234</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9613043377926273</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>0.2</v>
       </c>
+      <c r="B5" t="n">
+        <v>0.9992512048689527</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9968886171926915</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9924990417360295</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9827428434001153</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9486719184346725</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>0.25</v>
       </c>
+      <c r="B6" t="n">
+        <v>0.9988765653427398</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9958039810669504</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9888846927736189</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9746854073585255</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9270375282342874</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>0.3</v>
       </c>
+      <c r="B7" t="n">
+        <v>0.9985883376261169</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9945906216495096</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9830962318554399</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9678706954130689</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9003578705890455</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>0.35</v>
       </c>
+      <c r="B8" t="n">
+        <v>0.9981837652576282</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9933451233140028</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.9820136316876001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9546598591157085</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8854003677846179</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>0.4</v>
       </c>
+      <c r="B9" t="n">
+        <v>0.9971207306275235</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.990178862494807</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9793965707283891</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9442317997134787</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8860940305513804</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>0.45</v>
       </c>
+      <c r="B10" t="n">
+        <v>0.9964160042634529</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9890533438844092</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9798936040140763</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9509544460121131</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8809241698595225</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>0.5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.9954940897052277</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9882474011649347</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9740067446890124</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9519902555827144</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8929961750247483</v>
       </c>
     </row>
   </sheetData>
@@ -906,16 +1614,16 @@
         <v>0.1</v>
       </c>
       <c r="C1" t="n">
-        <v>1</v>
+        <v>0.3162277660168379</v>
       </c>
       <c r="D1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" t="n">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="F1" t="n">
         <v>10</v>
-      </c>
-      <c r="E1" t="n">
-        <v>100</v>
-      </c>
-      <c r="F1" t="n">
-        <v>1000</v>
       </c>
     </row>
     <row r="2">
@@ -923,7 +1631,19 @@
         <v>0.05</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01280752474491109</v>
+        <v>1.082558583980909</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.445409125941989</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.587528380535947</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4.356847306994929</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8.284633101977924</v>
       </c>
     </row>
     <row r="3">
@@ -931,7 +1651,19 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.03051621096480295</v>
+        <v>1.402506087263214</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2.542180422753122</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.439991387551512</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6.776192558294742</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12.94552064112126</v>
       </c>
     </row>
     <row r="4">
@@ -939,42 +1671,867 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.02596437303976673</v>
+        <v>1.910786643504728</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.650688954777815</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.523521616758619</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8.394508027510026</v>
+      </c>
+      <c r="F4" t="n">
+        <v>15.99113379349869</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>0.2</v>
       </c>
+      <c r="B5" t="n">
+        <v>2.217411214629755</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4.520922092166552</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.022113545041966</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10.65979353382531</v>
+      </c>
+      <c r="F5" t="n">
+        <v>18.43701052919879</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>0.25</v>
       </c>
+      <c r="B6" t="n">
+        <v>2.716140340598038</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5.250592643559267</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8.550695961766928</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12.91943583506906</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22.02236968804354</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>0.3</v>
       </c>
+      <c r="B7" t="n">
+        <v>3.044767623314493</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5.962210099833418</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10.54977181906008</v>
+      </c>
+      <c r="E7" t="n">
+        <v>14.56323984339752</v>
+      </c>
+      <c r="F7" t="n">
+        <v>25.7948523288252</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>0.35</v>
       </c>
+      <c r="B8" t="n">
+        <v>3.453737875682171</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6.613765294852695</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10.88334701867732</v>
+      </c>
+      <c r="E8" t="n">
+        <v>17.31943778970667</v>
+      </c>
+      <c r="F8" t="n">
+        <v>27.69916897532088</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>0.4</v>
       </c>
+      <c r="B9" t="n">
+        <v>4.348936218078419</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8.036641702043152</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11.6508036038237</v>
+      </c>
+      <c r="E9" t="n">
+        <v>19.22517147767938</v>
+      </c>
+      <c r="F9" t="n">
+        <v>27.61354481318591</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>0.45</v>
       </c>
+      <c r="B10" t="n">
+        <v>4.85233936202373</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8.485458972695305</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.50893449038672</v>
+      </c>
+      <c r="E10" t="n">
+        <v>18.01891555185344</v>
+      </c>
+      <c r="F10" t="n">
+        <v>28.24595280159718</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>0.5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5.441167685252715</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8.792873931665429</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13.09221742629819</v>
+      </c>
+      <c r="E11" t="n">
+        <v>17.82605970557525</v>
+      </c>
+      <c r="F11" t="n">
+        <v>26.74780639935186</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>r/C</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C1" t="n">
+        <v>0.3162277660168379</v>
+      </c>
+      <c r="D1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" t="n">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="F1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.0261023134416547</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.01835518633090683</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1052697627808836</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3786919507986806</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.278103082935415</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.05058343379179098</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.04988242150677635</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1884211008098857</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1457895000728531</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.101563241417391</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.07842750920425967</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0682263549342581</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2817105046754973</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1186466489891167</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.835549477087906</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.08214674779117814</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.07081236659483636</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2508861102335818</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1180586680315958</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.652681013132845</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.09635208854240185</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.09854354947882094</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.262450986849867</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.262858574036958</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.699869441846849</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1324318271365286</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1650241890755284</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4369348018073813</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.824924257271535</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.688025613815787</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.1116402010982451</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.1635104491536383</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4797508300789737</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7502229209159932</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.737128560668037</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.08603139626841561</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2646206084238703</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7211874819139394</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5983834906537364</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.855928220716919</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.09313269433583393</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2241235607951184</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5515496485679616</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.6117506677371924</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.519580333211767</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.08631762097918916</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1452023713275574</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.2667820952465743</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3960674448034105</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.05674606605317</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>r/C</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C1" t="n">
+        <v>0.3162277660168379</v>
+      </c>
+      <c r="D1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" t="n">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="F1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.04717159271240234</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.03211808204650879</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.03098845481872559</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.04518675804138184</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03431940078735352</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.03703951835632324</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0365452766418457</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.04681015014648438</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.03049135208129883</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.03028059005737305</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0720679759979248</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.03303933143615723</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.03607511520385742</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.05146217346191406</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.02476859092712402</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.03148770332336426</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.03363204002380371</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.03331589698791504</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.03139424324035645</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.03568220138549805</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0441744327545166</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.04290342330932617</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1215224266052246</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.03169536590576172</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03629636764526367</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.03322696685791016</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0419154167175293</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.03258609771728516</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.07359051704406738</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.02843928337097168</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.03229451179504395</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.03394484519958496</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.03833270072937012</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0344843864440918</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.02885532379150391</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.03948283195495605</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.03431081771850586</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.03217625617980957</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.08942866325378418</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.03273439407348633</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.03033018112182617</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0481107234954834</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.03035140037536621</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.04997920989990234</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.02764725685119629</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.04026412963867188</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.03938794136047363</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.04856586456298828</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.04830765724182129</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.03162932395935059</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>r/C</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C1" t="n">
+        <v>0.3162277660168379</v>
+      </c>
+      <c r="D1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" t="n">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="F1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.08690476417541504</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.06891608238220215</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.09052348136901855</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2154238224029541</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.254826545715332</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.2708189487457275</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.09356045722961426</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.08620095252990723</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2338216304779053</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1995069980621338</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.7204983234405518</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1111927032470703</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.08807229995727539</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.249955415725708</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1977977752685547</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.08792662620544434</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2316558361053467</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.09444904327392578</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1148991584777832</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.436678409576416</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.6342172622680664</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.09570503234863281</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1426413059234619</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1110095977783203</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2904539108276367</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1084079742431641</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.09238171577453613</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4558935165405273</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9113271236419678</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.153907299041748</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.09779810905456543</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.08462786674499512</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1328949928283691</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.2300245761871338</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5259358882904053</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1184108257293701</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.08308148384094238</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.09990453720092773</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1844489574432373</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4355967044830322</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1014840602874756</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1058907508850098</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.252593994140625</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.6480858325958252</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4827044010162354</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.1496496200561523</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1139349937438965</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4678418636322021</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2129383087158203</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6993377208709717</v>
       </c>
     </row>
   </sheetData>

--- a/result.xlsx
+++ b/result.xlsx
@@ -1697,7 +1697,7 @@
         <v>4.520922092166552</v>
       </c>
       <c r="D5" t="n">
-        <v>7.022113545041966</v>
+        <v>7.022113545041967</v>
       </c>
       <c r="E5" t="n">
         <v>10.65979353382531</v>
@@ -1800,7 +1800,7 @@
         <v>11.50893449038672</v>
       </c>
       <c r="E10" t="n">
-        <v>18.01891555185344</v>
+        <v>18.01891555185345</v>
       </c>
       <c r="F10" t="n">
         <v>28.24595280159718</v>
@@ -2103,19 +2103,19 @@
         <v>0.05</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04717159271240234</v>
+        <v>0.01333260536193848</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03211808204650879</v>
+        <v>0.008802413940429688</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03098845481872559</v>
+        <v>0.008630514144897461</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04518675804138184</v>
+        <v>0.008327007293701172</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03431940078735352</v>
+        <v>0.00835871696472168</v>
       </c>
     </row>
     <row r="3">
@@ -2123,19 +2123,19 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.03703951835632324</v>
+        <v>0.01196122169494629</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0365452766418457</v>
+        <v>0.01006364822387695</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04681015014648438</v>
+        <v>0.008813619613647461</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03049135208129883</v>
+        <v>0.008439064025878906</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03028059005737305</v>
+        <v>0.008513689041137695</v>
       </c>
     </row>
     <row r="4">
@@ -2143,19 +2143,19 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0720679759979248</v>
+        <v>0.008859395980834961</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03303933143615723</v>
+        <v>0.009678125381469727</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03607511520385742</v>
+        <v>0.008916378021240234</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05146217346191406</v>
+        <v>0.008892297744750977</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02476859092712402</v>
+        <v>0.008576631546020508</v>
       </c>
     </row>
     <row r="5">
@@ -2163,19 +2163,19 @@
         <v>0.2</v>
       </c>
       <c r="B5" t="n">
-        <v>0.03148770332336426</v>
+        <v>0.009215831756591797</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03363204002380371</v>
+        <v>0.008940458297729492</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03331589698791504</v>
+        <v>0.008748531341552734</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03139424324035645</v>
+        <v>0.008678913116455078</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03568220138549805</v>
+        <v>0.008874416351318359</v>
       </c>
     </row>
     <row r="6">
@@ -2183,19 +2183,19 @@
         <v>0.25</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0441744327545166</v>
+        <v>0.0111081600189209</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04290342330932617</v>
+        <v>0.01008963584899902</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1215224266052246</v>
+        <v>0.008760929107666016</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03169536590576172</v>
+        <v>0.008562803268432617</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03629636764526367</v>
+        <v>0.008695125579833984</v>
       </c>
     </row>
     <row r="7">
@@ -2203,19 +2203,19 @@
         <v>0.3</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03322696685791016</v>
+        <v>0.009675502777099609</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0419154167175293</v>
+        <v>0.008932828903198242</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03258609771728516</v>
+        <v>0.009030342102050781</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07359051704406738</v>
+        <v>0.00885772705078125</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02843928337097168</v>
+        <v>0.008664846420288086</v>
       </c>
     </row>
     <row r="8">
@@ -2223,19 +2223,19 @@
         <v>0.35</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03229451179504395</v>
+        <v>0.009645700454711914</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03394484519958496</v>
+        <v>0.008963108062744141</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03833270072937012</v>
+        <v>0.009064197540283203</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0344843864440918</v>
+        <v>0.008706808090209961</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02885532379150391</v>
+        <v>0.008890628814697266</v>
       </c>
     </row>
     <row r="9">
@@ -2243,19 +2243,19 @@
         <v>0.4</v>
       </c>
       <c r="B9" t="n">
-        <v>0.03948283195495605</v>
+        <v>0.008936882019042969</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03431081771850586</v>
+        <v>0.009049415588378906</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03217625617980957</v>
+        <v>0.009286165237426758</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08942866325378418</v>
+        <v>0.008829116821289062</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03273439407348633</v>
+        <v>0.009003162384033203</v>
       </c>
     </row>
     <row r="10">
@@ -2263,19 +2263,19 @@
         <v>0.45</v>
       </c>
       <c r="B10" t="n">
-        <v>0.03033018112182617</v>
+        <v>0.01341509819030762</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0481107234954834</v>
+        <v>0.009080886840820312</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03035140037536621</v>
+        <v>0.009052753448486328</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04997920989990234</v>
+        <v>0.009005546569824219</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02764725685119629</v>
+        <v>0.008813142776489258</v>
       </c>
     </row>
     <row r="11">
@@ -2283,19 +2283,19 @@
         <v>0.5</v>
       </c>
       <c r="B11" t="n">
-        <v>0.04026412963867188</v>
+        <v>0.009002685546875</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03938794136047363</v>
+        <v>0.009055137634277344</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04856586456298828</v>
+        <v>0.008974075317382812</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04830765724182129</v>
+        <v>0.009016036987304688</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03162932395935059</v>
+        <v>0.008992433547973633</v>
       </c>
     </row>
   </sheetData>
@@ -2339,19 +2339,19 @@
         <v>0.05</v>
       </c>
       <c r="B2" t="n">
-        <v>0.08690476417541504</v>
+        <v>0.0436551570892334</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06891608238220215</v>
+        <v>0.0312492847442627</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09052348136901855</v>
+        <v>0.04453802108764648</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2154238224029541</v>
+        <v>0.1090290546417236</v>
       </c>
       <c r="F2" t="n">
-        <v>0.254826545715332</v>
+        <v>0.220325231552124</v>
       </c>
     </row>
     <row r="3">
@@ -2359,19 +2359,19 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2708189487457275</v>
+        <v>0.04256153106689453</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09356045722961426</v>
+        <v>0.0373995304107666</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08620095252990723</v>
+        <v>0.03798675537109375</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2338216304779053</v>
+        <v>0.05816745758056641</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1995069980621338</v>
+        <v>0.1214132308959961</v>
       </c>
     </row>
     <row r="4">
@@ -2379,19 +2379,19 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7204983234405518</v>
+        <v>0.08876299858093262</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1111927032470703</v>
+        <v>0.04379749298095703</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08807229995727539</v>
+        <v>0.05591249465942383</v>
       </c>
       <c r="E4" t="n">
-        <v>0.249955415725708</v>
+        <v>0.05888867378234863</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1977977752685547</v>
+        <v>0.125767707824707</v>
       </c>
     </row>
     <row r="5">
@@ -2399,19 +2399,19 @@
         <v>0.2</v>
       </c>
       <c r="B5" t="n">
-        <v>0.08792662620544434</v>
+        <v>0.04161977767944336</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2316558361053467</v>
+        <v>0.03592467308044434</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09444904327392578</v>
+        <v>0.0489203929901123</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1148991584777832</v>
+        <v>0.05182409286499023</v>
       </c>
       <c r="F5" t="n">
-        <v>0.436678409576416</v>
+        <v>0.1653640270233154</v>
       </c>
     </row>
     <row r="6">
@@ -2419,19 +2419,19 @@
         <v>0.25</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6342172622680664</v>
+        <v>0.04495358467102051</v>
       </c>
       <c r="C6" t="n">
-        <v>0.09570503234863281</v>
+        <v>0.03601789474487305</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1426413059234619</v>
+        <v>0.05052947998046875</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1110095977783203</v>
+        <v>0.09883236885070801</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2904539108276367</v>
+        <v>0.1979501247406006</v>
       </c>
     </row>
     <row r="7">
@@ -2439,19 +2439,19 @@
         <v>0.3</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1084079742431641</v>
+        <v>0.0603935718536377</v>
       </c>
       <c r="C7" t="n">
-        <v>0.09238171577453613</v>
+        <v>0.03232336044311523</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4558935165405273</v>
+        <v>0.09262752532958984</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9113271236419678</v>
+        <v>0.06763410568237305</v>
       </c>
       <c r="F7" t="n">
-        <v>0.153907299041748</v>
+        <v>0.1020081043243408</v>
       </c>
     </row>
     <row r="8">
@@ -2459,19 +2459,19 @@
         <v>0.35</v>
       </c>
       <c r="B8" t="n">
-        <v>0.09779810905456543</v>
+        <v>0.07912492752075195</v>
       </c>
       <c r="C8" t="n">
-        <v>0.08462786674499512</v>
+        <v>0.03850412368774414</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1328949928283691</v>
+        <v>0.05677938461303711</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2300245761871338</v>
+        <v>0.1043179035186768</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5259358882904053</v>
+        <v>0.3868668079376221</v>
       </c>
     </row>
     <row r="9">
@@ -2479,19 +2479,19 @@
         <v>0.4</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1184108257293701</v>
+        <v>0.05436158180236816</v>
       </c>
       <c r="C9" t="n">
-        <v>0.08308148384094238</v>
+        <v>0.03858804702758789</v>
       </c>
       <c r="D9" t="n">
-        <v>0.09990453720092773</v>
+        <v>0.05736613273620605</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1844489574432373</v>
+        <v>0.09073042869567871</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4355967044830322</v>
+        <v>0.2211983203887939</v>
       </c>
     </row>
     <row r="10">
@@ -2499,19 +2499,19 @@
         <v>0.45</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1014840602874756</v>
+        <v>0.04832839965820312</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1058907508850098</v>
+        <v>0.0573883056640625</v>
       </c>
       <c r="D10" t="n">
-        <v>0.252593994140625</v>
+        <v>0.05117225646972656</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6480858325958252</v>
+        <v>0.09003090858459473</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4827044010162354</v>
+        <v>0.3462610244750977</v>
       </c>
     </row>
     <row r="11">
@@ -2519,19 +2519,19 @@
         <v>0.5</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1496496200561523</v>
+        <v>0.04442024230957031</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1139349937438965</v>
+        <v>0.06989884376525879</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4678418636322021</v>
+        <v>0.07161927223205566</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2129383087158203</v>
+        <v>0.09449577331542969</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6993377208709717</v>
+        <v>0.4592134952545166</v>
       </c>
     </row>
   </sheetData>
